--- a/exports/trend_1d/ALKEM_full_report.xlsx
+++ b/exports/trend_1d/ALKEM_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:U65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>9.49</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42388</v>
+        <v>42389</v>
       </c>
       <c r="H2" t="n">
-        <v>1330.4</v>
+        <v>1322.8</v>
       </c>
       <c r="I2" t="n">
         <v>1328.045</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K2" t="n">
-        <v>-9.33</v>
+        <v>-9.85</v>
       </c>
       <c r="L2" t="n">
         <v>12.7</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>16.84</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42457</v>
+        <v>42458</v>
       </c>
       <c r="H3" t="n">
-        <v>1387.3</v>
+        <v>1410.35</v>
       </c>
       <c r="I3" t="n">
         <v>1402.92414361839</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.88</v>
+        <v>-6.62</v>
       </c>
       <c r="L3" t="n">
         <v>8.17</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>10.94</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42480</v>
+        <v>42481</v>
       </c>
       <c r="H4" t="n">
-        <v>1273.1</v>
+        <v>1242.05</v>
       </c>
       <c r="I4" t="n">
         <v>1262.955107234339</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>-9.73</v>
+        <v>-11.93</v>
       </c>
       <c r="L4" t="n">
-        <v>12.33</v>
+        <v>14.25</v>
       </c>
       <c r="M4" t="n">
         <v>5.49</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>12.32</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42522</v>
+        <v>42523</v>
       </c>
       <c r="H5" t="n">
-        <v>1288.05</v>
+        <v>1305.95</v>
       </c>
       <c r="I5" t="n">
         <v>1299.397290994887</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.7</v>
+        <v>-5.14</v>
       </c>
       <c r="L5" t="n">
-        <v>4.21</v>
+        <v>5.76</v>
       </c>
       <c r="M5" t="n">
         <v>1.56</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.17</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42669</v>
+        <v>42670</v>
       </c>
       <c r="H6" t="n">
-        <v>1662.45</v>
+        <v>1618.4</v>
       </c>
       <c r="I6" t="n">
         <v>1624.913016770136</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K6" t="n">
-        <v>27.3</v>
+        <v>23.93</v>
       </c>
       <c r="L6" t="n">
         <v>2.13</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>9.960000000000001</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42767</v>
+        <v>42768</v>
       </c>
       <c r="H7" t="n">
-        <v>1694.75</v>
+        <v>1770.5</v>
       </c>
       <c r="I7" t="n">
         <v>1711.000043187632</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.72</v>
+        <v>-9.4</v>
       </c>
       <c r="L7" t="n">
-        <v>8.779999999999999</v>
+        <v>11.14</v>
       </c>
       <c r="M7" t="n">
         <v>2.33</v>
       </c>
       <c r="N7" t="n">
-        <v>3.97</v>
+        <v>4.47</v>
       </c>
       <c r="O7" t="n">
         <v>-2.65</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42804</v>
+        <v>42808</v>
       </c>
       <c r="H8" t="n">
-        <v>1977.75</v>
+        <v>1930.5</v>
       </c>
       <c r="I8" t="n">
         <v>1950.539397794859</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K8" t="n">
-        <v>11.71</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="L8" t="n">
         <v>4.76</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>11.87</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42815</v>
+        <v>42816</v>
       </c>
       <c r="H9" t="n">
-        <v>2134.15</v>
+        <v>2170.35</v>
       </c>
       <c r="I9" t="n">
         <v>2155.424835468855</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>-10.55</v>
+        <v>-12.42</v>
       </c>
       <c r="L9" t="n">
-        <v>12.35</v>
+        <v>12.87</v>
       </c>
       <c r="M9" t="n">
         <v>0.8</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>11.84</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42849</v>
+        <v>42850</v>
       </c>
       <c r="H10" t="n">
-        <v>2021.7</v>
+        <v>1984.8</v>
       </c>
       <c r="I10" t="n">
         <v>2011.960822696013</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.85</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>7.9</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="M10" t="n">
         <v>1.11</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>14.62</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43003</v>
+        <v>43004</v>
       </c>
       <c r="H11" t="n">
-        <v>1845.55</v>
+        <v>1880.65</v>
       </c>
       <c r="I11" t="n">
         <v>1869.318896672263</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K11" t="n">
-        <v>7.02</v>
+        <v>5.25</v>
       </c>
       <c r="L11" t="n">
         <v>2.72</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>13.18</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43178</v>
+        <v>43179</v>
       </c>
       <c r="H12" t="n">
-        <v>2141.35</v>
+        <v>2104.1</v>
       </c>
       <c r="I12" t="n">
         <v>2118.192598604241</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K12" t="n">
-        <v>13.86</v>
+        <v>11.88</v>
       </c>
       <c r="L12" t="n">
         <v>7.21</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>8.52</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43214</v>
+        <v>43215</v>
       </c>
       <c r="H13" t="n">
-        <v>1924.6</v>
+        <v>1934.7</v>
       </c>
       <c r="I13" t="n">
         <v>1929.000831272205</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K13" t="n">
-        <v>8.529999999999999</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="L13" t="n">
         <v>2.18</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>9.699999999999999</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43298</v>
+        <v>43299</v>
       </c>
       <c r="H14" t="n">
-        <v>1853.9</v>
+        <v>1832.95</v>
       </c>
       <c r="I14" t="n">
         <v>1843.921778620885</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.18</v>
+        <v>-5.26</v>
       </c>
       <c r="L14" t="n">
         <v>6.66</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>10.84</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43304</v>
+        <v>43305</v>
       </c>
       <c r="H15" t="n">
-        <v>1881.25</v>
+        <v>2024</v>
       </c>
       <c r="I15" t="n">
         <v>2011.006640024322</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.64</v>
+        <v>-10.42</v>
       </c>
       <c r="L15" t="n">
-        <v>3.51</v>
+        <v>14.46</v>
       </c>
       <c r="M15" t="n">
         <v>0.75</v>
       </c>
       <c r="N15" t="n">
-        <v>2.14</v>
+        <v>7.59</v>
       </c>
       <c r="O15" t="n">
         <v>-1.13</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>13.6</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43381</v>
+        <v>43382</v>
       </c>
       <c r="H16" t="n">
-        <v>1968.6</v>
+        <v>1902.95</v>
       </c>
       <c r="I16" t="n">
         <v>1966.969401833624</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.74</v>
+        <v>-5.98</v>
       </c>
       <c r="L16" t="n">
-        <v>7.85</v>
+        <v>8.6</v>
       </c>
       <c r="M16" t="n">
         <v>1.89</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>12.9</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43473</v>
+        <v>43474</v>
       </c>
       <c r="H17" t="n">
-        <v>1954.7</v>
+        <v>1975.45</v>
       </c>
       <c r="I17" t="n">
         <v>1975.425213473287</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.72</v>
+        <v>-3.81</v>
       </c>
       <c r="L17" t="n">
         <v>5.11</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>6.14</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43507</v>
+        <v>43508</v>
       </c>
       <c r="H18" t="n">
-        <v>1891.7</v>
+        <v>1839.95</v>
       </c>
       <c r="I18" t="n">
         <v>1854.774442963121</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.24</v>
+        <v>-6.86</v>
       </c>
       <c r="L18" t="n">
-        <v>6.96</v>
+        <v>7.11</v>
       </c>
       <c r="M18" t="n">
         <v>2.29</v>
       </c>
       <c r="N18" t="n">
-        <v>1.77</v>
+        <v>2.74</v>
       </c>
       <c r="O18" t="n">
         <v>1.06</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,25 +1730,25 @@
         <v>9.17</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43615</v>
+        <v>43616</v>
       </c>
       <c r="H19" t="n">
-        <v>1760.15</v>
+        <v>1794.35</v>
       </c>
       <c r="I19" t="n">
         <v>1786.874665263986</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K19" t="n">
-        <v>4.34</v>
+        <v>2.48</v>
       </c>
       <c r="L19" t="n">
         <v>8</v>
       </c>
       <c r="M19" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
         <v>2.37</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>7.5</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43643</v>
+        <v>43644</v>
       </c>
       <c r="H20" t="n">
-        <v>1682.5</v>
+        <v>1669</v>
       </c>
       <c r="I20" t="n">
         <v>1669.515205866896</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.23</v>
+        <v>-6.99</v>
       </c>
       <c r="L20" t="n">
-        <v>6.37</v>
+        <v>7.43</v>
       </c>
       <c r="M20" t="n">
         <v>1.55</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>9.74</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43703</v>
+        <v>43704</v>
       </c>
       <c r="H21" t="n">
-        <v>1789.6</v>
+        <v>1826.9</v>
       </c>
       <c r="I21" t="n">
         <v>1821.294045148458</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K21" t="n">
-        <v>-7.23</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="L21" t="n">
         <v>10.01</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>10.03</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43901</v>
+        <v>43902</v>
       </c>
       <c r="H22" t="n">
-        <v>2590.95</v>
+        <v>2386.5</v>
       </c>
       <c r="I22" t="n">
         <v>2406.676424355675</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K22" t="n">
-        <v>41.82</v>
+        <v>30.63</v>
       </c>
       <c r="L22" t="n">
         <v>2.36</v>
@@ -1695,7 +1958,7 @@
         <v>3.05</v>
       </c>
       <c r="N22" t="n">
-        <v>3.5</v>
+        <v>7.89</v>
       </c>
       <c r="O22" t="n">
         <v>2.08</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>8</v>
+      </c>
+      <c r="U22" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>15.32</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43936</v>
+        <v>43937</v>
       </c>
       <c r="H23" t="n">
-        <v>2686.85</v>
+        <v>2757.85</v>
       </c>
       <c r="I23" t="n">
         <v>2751.999736513475</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K23" t="n">
-        <v>-12.59</v>
+        <v>-15.56</v>
       </c>
       <c r="L23" t="n">
         <v>20.64</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>19.18</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43977</v>
+        <v>43978</v>
       </c>
       <c r="H24" t="n">
-        <v>2411.85</v>
+        <v>2299.15</v>
       </c>
       <c r="I24" t="n">
         <v>2315.462166455754</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K24" t="n">
-        <v>-12.55</v>
+        <v>-16.63</v>
       </c>
       <c r="L24" t="n">
-        <v>15.3</v>
+        <v>19.43</v>
       </c>
       <c r="M24" t="n">
         <v>0.71</v>
       </c>
       <c r="N24" t="n">
-        <v>4.58</v>
+        <v>4.67</v>
       </c>
       <c r="O24" t="n">
         <v>2.64</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>16.15</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44026</v>
+        <v>44027</v>
       </c>
       <c r="H25" t="n">
-        <v>2474.9</v>
+        <v>2536.25</v>
       </c>
       <c r="I25" t="n">
         <v>2513.249199630986</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K25" t="n">
-        <v>-7.64</v>
+        <v>-10.31</v>
       </c>
       <c r="L25" t="n">
-        <v>9.18</v>
+        <v>10.61</v>
       </c>
       <c r="M25" t="n">
         <v>1.48</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>9.17</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44119</v>
+        <v>44120</v>
       </c>
       <c r="H26" t="n">
-        <v>2659.35</v>
+        <v>2650.55</v>
       </c>
       <c r="I26" t="n">
         <v>2657.730310124013</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K26" t="n">
-        <v>4.85</v>
+        <v>4.51</v>
       </c>
       <c r="L26" t="n">
         <v>4.78</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>8.16</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44159</v>
+        <v>44160</v>
       </c>
       <c r="H27" t="n">
-        <v>2775.65</v>
+        <v>2798.1</v>
       </c>
       <c r="I27" t="n">
         <v>2783.226091731128</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.72</v>
+        <v>-5.57</v>
       </c>
       <c r="L27" t="n">
-        <v>6.02</v>
+        <v>6.2</v>
       </c>
       <c r="M27" t="n">
         <v>1.22</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>6.42</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44235</v>
+        <v>44236</v>
       </c>
       <c r="H28" t="n">
-        <v>2901.95</v>
+        <v>2875.5</v>
       </c>
       <c r="I28" t="n">
         <v>2893.123070561561</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K28" t="n">
-        <v>3.71</v>
+        <v>2.77</v>
       </c>
       <c r="L28" t="n">
         <v>1.32</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44294</v>
+        <v>44295</v>
       </c>
       <c r="H29" t="n">
-        <v>2706.45</v>
+        <v>2832.3</v>
       </c>
       <c r="I29" t="n">
         <v>2807.956691760726</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K29" t="n">
-        <v>5.88</v>
+        <v>1.5</v>
       </c>
       <c r="L29" t="n">
         <v>2.97</v>
@@ -2094,7 +2441,7 @@
         <v>3.12</v>
       </c>
       <c r="N29" t="n">
-        <v>3.87</v>
+        <v>4.65</v>
       </c>
       <c r="O29" t="n">
         <v>-0.91</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>10.32</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44491</v>
+        <v>44494</v>
       </c>
       <c r="H30" t="n">
-        <v>3747.25</v>
+        <v>3707.75</v>
       </c>
       <c r="I30" t="n">
         <v>3717.332213212545</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K30" t="n">
-        <v>32.3</v>
+        <v>30.91</v>
       </c>
       <c r="L30" t="n">
         <v>5.32</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>7</v>
+      </c>
+      <c r="U30" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>8.24</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44559</v>
+        <v>44560</v>
       </c>
       <c r="H31" t="n">
-        <v>3517.75</v>
+        <v>3624</v>
       </c>
       <c r="I31" t="n">
         <v>3605.698574546037</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K31" t="n">
-        <v>5.12</v>
+        <v>2.26</v>
       </c>
       <c r="L31" t="n">
         <v>1.91</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>8.65</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44586</v>
+        <v>44588</v>
       </c>
       <c r="H32" t="n">
-        <v>3454</v>
+        <v>3380.7</v>
       </c>
       <c r="I32" t="n">
         <v>3450.268642764731</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K32" t="n">
-        <v>-4.69</v>
+        <v>-6.71</v>
       </c>
       <c r="L32" t="n">
-        <v>6.18</v>
+        <v>7.6</v>
       </c>
       <c r="M32" t="n">
         <v>1.28</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>9.449999999999999</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44637</v>
+        <v>44641</v>
       </c>
       <c r="H33" t="n">
-        <v>3438.95</v>
+        <v>3496.85</v>
       </c>
       <c r="I33" t="n">
         <v>3483.790109321113</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.72</v>
+        <v>-3.44</v>
       </c>
       <c r="L33" t="n">
         <v>6.49</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,25 +2765,25 @@
         <v>9.07</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44673</v>
+        <v>44676</v>
       </c>
       <c r="H34" t="n">
-        <v>3370.7</v>
+        <v>3310.95</v>
       </c>
       <c r="I34" t="n">
         <v>3355.734783615119</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K34" t="n">
-        <v>-3.61</v>
+        <v>-5.32</v>
       </c>
       <c r="L34" t="n">
-        <v>4.13</v>
+        <v>5.49</v>
       </c>
       <c r="M34" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N34" t="n">
         <v>3.52</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>8.42</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44757</v>
+        <v>44760</v>
       </c>
       <c r="H35" t="n">
-        <v>3211.95</v>
+        <v>3250.1</v>
       </c>
       <c r="I35" t="n">
         <v>3229.818743228601</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K35" t="n">
-        <v>2.99</v>
+        <v>1.84</v>
       </c>
       <c r="L35" t="n">
         <v>1.36</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>7.77</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44778</v>
+        <v>44781</v>
       </c>
       <c r="H36" t="n">
-        <v>3112.8</v>
+        <v>2984.45</v>
       </c>
       <c r="I36" t="n">
         <v>3045.324593445025</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K36" t="n">
-        <v>-4.22</v>
+        <v>-8.17</v>
       </c>
       <c r="L36" t="n">
-        <v>6.24</v>
+        <v>9.66</v>
       </c>
       <c r="M36" t="n">
-        <v>0.36</v>
+        <v>2.5</v>
       </c>
       <c r="N36" t="n">
-        <v>2.68</v>
+        <v>4.12</v>
       </c>
       <c r="O36" t="n">
         <v>1.19</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>10.27</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44810</v>
+        <v>44811</v>
       </c>
       <c r="H37" t="n">
-        <v>3048.2</v>
+        <v>3102.2</v>
       </c>
       <c r="I37" t="n">
         <v>3074.566706186732</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.14</v>
+        <v>-3.95</v>
       </c>
       <c r="L37" t="n">
-        <v>2.54</v>
+        <v>4.21</v>
       </c>
       <c r="M37" t="n">
         <v>0.52</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>6.99</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44852</v>
+        <v>44853</v>
       </c>
       <c r="H38" t="n">
-        <v>3106.3</v>
+        <v>3079.9</v>
       </c>
       <c r="I38" t="n">
         <v>3102.173156206197</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K38" t="n">
-        <v>0.13</v>
+        <v>-0.72</v>
       </c>
       <c r="L38" t="n">
         <v>2.31</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>8.039999999999999</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44964</v>
+        <v>44965</v>
       </c>
       <c r="H39" t="n">
-        <v>3069.55</v>
+        <v>3180.8</v>
       </c>
       <c r="I39" t="n">
         <v>3159.410051856651</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K39" t="n">
-        <v>0.34</v>
+        <v>-3.28</v>
       </c>
       <c r="L39" t="n">
         <v>7.96</v>
@@ -2664,7 +3131,7 @@
         <v>1.16</v>
       </c>
       <c r="N39" t="n">
-        <v>2.61</v>
+        <v>3.62</v>
       </c>
       <c r="O39" t="n">
         <v>-0.85</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>5</v>
+      </c>
+      <c r="U39" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>7.66</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44995</v>
+        <v>44998</v>
       </c>
       <c r="H40" t="n">
-        <v>3145.85</v>
+        <v>3066.65</v>
       </c>
       <c r="I40" t="n">
         <v>3096.344994943349</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.1</v>
+        <v>-3.59</v>
       </c>
       <c r="L40" t="n">
-        <v>4.07</v>
+        <v>4.35</v>
       </c>
       <c r="M40" t="n">
         <v>1.2</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>7.8</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45013</v>
+        <v>45014</v>
       </c>
       <c r="H41" t="n">
-        <v>3240.8</v>
+        <v>3300.3</v>
       </c>
       <c r="I41" t="n">
         <v>3284.426380524651</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K41" t="n">
-        <v>-5.68</v>
+        <v>-7.62</v>
       </c>
       <c r="L41" t="n">
-        <v>6.47</v>
+        <v>7.97</v>
       </c>
       <c r="M41" t="n">
         <v>1.08</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>7.8</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45062</v>
+        <v>45063</v>
       </c>
       <c r="H42" t="n">
-        <v>3413.65</v>
+        <v>3383.95</v>
       </c>
       <c r="I42" t="n">
         <v>3398.507821216803</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K42" t="n">
-        <v>3.43</v>
+        <v>2.53</v>
       </c>
       <c r="L42" t="n">
         <v>2.13</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>6.77</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45105</v>
+        <v>45107</v>
       </c>
       <c r="H43" t="n">
-        <v>3446.15</v>
+        <v>3512.85</v>
       </c>
       <c r="I43" t="n">
         <v>3483.080233870874</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.84</v>
+        <v>-3.81</v>
       </c>
       <c r="L43" t="n">
-        <v>2.25</v>
+        <v>3.95</v>
       </c>
       <c r="M43" t="n">
         <v>1.08</v>
       </c>
       <c r="N43" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="O43" t="n">
         <v>-0.87</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>6.56</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45148</v>
+        <v>45149</v>
       </c>
       <c r="H44" t="n">
-        <v>4141.4</v>
+        <v>3822.1</v>
       </c>
       <c r="I44" t="n">
         <v>3906.370029383122</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K44" t="n">
-        <v>17.89</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L44" t="n">
         <v>2.02</v>
       </c>
       <c r="M44" t="n">
-        <v>0.58</v>
+        <v>0.99</v>
       </c>
       <c r="N44" t="n">
-        <v>2.03</v>
+        <v>7.71</v>
       </c>
       <c r="O44" t="n">
         <v>1.94</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>13.14</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45229</v>
+        <v>45230</v>
       </c>
       <c r="H45" t="n">
-        <v>3691.75</v>
+        <v>3721.85</v>
       </c>
       <c r="I45" t="n">
         <v>3718.501241238293</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K45" t="n">
-        <v>3.41</v>
+        <v>2.62</v>
       </c>
       <c r="L45" t="n">
         <v>7.87</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>6.11</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45308</v>
+        <v>45309</v>
       </c>
       <c r="H46" t="n">
-        <v>5056.15</v>
+        <v>4933.85</v>
       </c>
       <c r="I46" t="n">
         <v>4934.025924151995</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K46" t="n">
-        <v>35.85</v>
+        <v>32.56</v>
       </c>
       <c r="L46" t="n">
         <v>1.23</v>
@@ -3063,7 +3614,7 @@
         <v>0.41</v>
       </c>
       <c r="N46" t="n">
-        <v>1.91</v>
+        <v>2.42</v>
       </c>
       <c r="O46" t="n">
         <v>0.82</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>8.25</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45329</v>
+        <v>45330</v>
       </c>
       <c r="H47" t="n">
-        <v>5127.85</v>
+        <v>5311.15</v>
       </c>
       <c r="I47" t="n">
         <v>5225.120328081458</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.93</v>
+        <v>-7.65</v>
       </c>
       <c r="L47" t="n">
-        <v>5.9</v>
+        <v>8.99</v>
       </c>
       <c r="M47" t="n">
         <v>1.67</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>10.42</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H48" t="n">
-        <v>5056.8</v>
+        <v>4945.65</v>
       </c>
       <c r="I48" t="n">
         <v>4966.326002754359</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.79</v>
+        <v>-6.88</v>
       </c>
       <c r="L48" t="n">
         <v>12.28</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>9.65</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45415</v>
+        <v>45418</v>
       </c>
       <c r="H49" t="n">
-        <v>4904</v>
+        <v>5148.95</v>
       </c>
       <c r="I49" t="n">
         <v>4958.010232777315</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K49" t="n">
-        <v>0.84</v>
+        <v>-4.11</v>
       </c>
       <c r="L49" t="n">
-        <v>3.03</v>
+        <v>4.29</v>
       </c>
       <c r="M49" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="N49" t="n">
-        <v>4.43</v>
+        <v>4.99</v>
       </c>
       <c r="O49" t="n">
         <v>-2.2</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>10.74</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45441</v>
+        <v>45442</v>
       </c>
       <c r="H50" t="n">
-        <v>5262.45</v>
+        <v>4946.8</v>
       </c>
       <c r="I50" t="n">
         <v>5017.798181406311</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K50" t="n">
-        <v>2.2</v>
+        <v>-3.93</v>
       </c>
       <c r="L50" t="n">
         <v>5.22</v>
       </c>
       <c r="M50" t="n">
-        <v>0.26</v>
+        <v>2.71</v>
       </c>
       <c r="N50" t="n">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="O50" t="n">
         <v>4.99</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>12.54</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45481</v>
+        <v>45482</v>
       </c>
       <c r="H51" t="n">
-        <v>5221.85</v>
+        <v>5324.15</v>
       </c>
       <c r="I51" t="n">
         <v>5230.660750138043</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K51" t="n">
-        <v>-5.56</v>
+        <v>-7.63</v>
       </c>
       <c r="L51" t="n">
-        <v>6.31</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="M51" t="n">
         <v>0.71</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45587</v>
+        <v>45588</v>
       </c>
       <c r="H52" t="n">
-        <v>6110.25</v>
+        <v>5854.55</v>
       </c>
       <c r="I52" t="n">
         <v>5982.397810966248</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K52" t="n">
-        <v>14.76</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="L52" t="n">
         <v>5.52</v>
@@ -3405,7 +4028,7 @@
         <v>1.81</v>
       </c>
       <c r="N52" t="n">
-        <v>2.73</v>
+        <v>4.18</v>
       </c>
       <c r="O52" t="n">
         <v>1.96</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>4</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>11.6</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H53" t="n">
-        <v>4979</v>
+        <v>5052.55</v>
       </c>
       <c r="I53" t="n">
         <v>4991.651150561408</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="K53" t="n">
-        <v>14.96</v>
+        <v>13.7</v>
       </c>
       <c r="L53" t="n">
         <v>5.65</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>6</v>
+      </c>
+      <c r="U53" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>7.86</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45811</v>
+        <v>45812</v>
       </c>
       <c r="H54" t="n">
-        <v>4996.5</v>
+        <v>4868.5</v>
       </c>
       <c r="I54" t="n">
         <v>4919.816862579431</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.11</v>
+        <v>-3.64</v>
       </c>
       <c r="L54" t="n">
         <v>8.720000000000001</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>9.619999999999999</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45863</v>
+        <v>45866</v>
       </c>
       <c r="H55" t="n">
-        <v>5011.9</v>
+        <v>5047.4</v>
       </c>
       <c r="I55" t="n">
         <v>5021.255815841879</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.95</v>
+        <v>-3.67</v>
       </c>
       <c r="L55" t="n">
-        <v>3.69</v>
+        <v>4.24</v>
       </c>
       <c r="M55" t="n">
         <v>1</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>5.52</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45876</v>
+        <v>45877</v>
       </c>
       <c r="H56" t="n">
-        <v>4872</v>
+        <v>4764</v>
       </c>
       <c r="I56" t="n">
         <v>4828.840974949122</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.48</v>
+        <v>-5.61</v>
       </c>
       <c r="L56" t="n">
-        <v>5.05</v>
+        <v>5.89</v>
       </c>
       <c r="M56" t="n">
         <v>0.62</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>7.37</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45880</v>
+        <v>45881</v>
       </c>
       <c r="H57" t="n">
-        <v>4844.5</v>
+        <v>5149</v>
       </c>
       <c r="I57" t="n">
         <v>5110.106172756971</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.69</v>
+        <v>-8.08</v>
       </c>
       <c r="L57" t="n">
-        <v>2.28</v>
+        <v>9.31</v>
       </c>
       <c r="M57" t="n">
-        <v>0.12</v>
+        <v>0.41</v>
       </c>
       <c r="N57" t="n">
-        <v>1.69</v>
+        <v>6.29</v>
       </c>
       <c r="O57" t="n">
         <v>-2.22</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>10.28</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="H58" t="n">
-        <v>5870.5</v>
+        <v>5402.5</v>
       </c>
       <c r="I58" t="n">
         <v>5517.03148347057</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K58" t="n">
-        <v>14.01</v>
+        <v>4.92</v>
       </c>
       <c r="L58" t="n">
         <v>6.35</v>
@@ -3747,7 +4442,7 @@
         <v>0.97</v>
       </c>
       <c r="N58" t="n">
-        <v>1.98</v>
+        <v>7.97</v>
       </c>
       <c r="O58" t="n">
         <v>6.29</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>7</v>
+      </c>
+      <c r="U58" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>13.13</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="H59" t="n">
-        <v>5582</v>
+        <v>5642</v>
       </c>
       <c r="I59" t="n">
         <v>5592.854338427089</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K59" t="n">
-        <v>-3.32</v>
+        <v>-4.43</v>
       </c>
       <c r="L59" t="n">
         <v>8.279999999999999</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>8.66</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="H60" t="n">
-        <v>5520.5</v>
+        <v>5235</v>
       </c>
       <c r="I60" t="n">
         <v>5238.417783948008</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K60" t="n">
-        <v>-2.15</v>
+        <v>-7.21</v>
       </c>
       <c r="L60" t="n">
-        <v>3.71</v>
+        <v>7.95</v>
       </c>
       <c r="M60" t="n">
         <v>1.45</v>
       </c>
       <c r="N60" t="n">
-        <v>1.89</v>
+        <v>5.17</v>
       </c>
       <c r="O60" t="n">
         <v>1.07</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>13.05</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="H61" t="n">
-        <v>5659</v>
+        <v>5709</v>
       </c>
       <c r="I61" t="n">
         <v>5683.615689366406</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K61" t="n">
-        <v>-8.1</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="L61" t="n">
         <v>10.58</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>6.62</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="H62" t="n">
-        <v>5449.5</v>
+        <v>5368</v>
       </c>
       <c r="I62" t="n">
         <v>5432.040311863298</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K62" t="n">
-        <v>-4.55</v>
+        <v>-5.97</v>
       </c>
       <c r="L62" t="n">
-        <v>5.31</v>
+        <v>9.35</v>
       </c>
       <c r="M62" t="n">
         <v>1.38</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>6.49</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="H63" t="n">
-        <v>5348.5</v>
+        <v>5466.5</v>
       </c>
       <c r="I63" t="n">
         <v>5383.495959480436</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K63" t="n">
-        <v>0.36</v>
+        <v>-1.83</v>
       </c>
       <c r="L63" t="n">
         <v>2.65</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="H64" t="n">
-        <v>5050</v>
+        <v>5004</v>
       </c>
       <c r="I64" t="n">
         <v>5022.105000984886</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K64" t="n">
-        <v>-7.62</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="L64" t="n">
-        <v>7.77</v>
+        <v>8.98</v>
       </c>
       <c r="M64" t="n">
         <v>1.31</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4149,6 +4928,14 @@
       <c r="Q65" t="n">
         <v>7</v>
       </c>
+      <c r="R65" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8733,7 +9520,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61.1</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="6">
@@ -8743,7 +9530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -8753,7 +9540,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8">
@@ -8763,7 +9550,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -8773,7 +9560,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80.5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10">
@@ -8783,7 +9570,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -8793,7 +9580,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -8803,7 +9590,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -8813,7 +9600,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="14">
@@ -8823,7 +9610,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.37</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="15">
@@ -8833,7 +9620,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.08</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="16">
@@ -8843,7 +9630,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.44</v>
+        <v>-3.86</v>
       </c>
     </row>
     <row r="17">
@@ -8853,7 +9640,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>41.82</v>
+        <v>32.56</v>
       </c>
     </row>
     <row r="18">
@@ -8863,7 +9650,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>39.7</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="19">
@@ -8873,7 +9660,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.05</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="20">
@@ -8883,7 +9670,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.65</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="21">
@@ -8903,7 +9690,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
@@ -8913,7 +9700,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -8923,7 +9710,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="25">
@@ -8943,7 +9730,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.58</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="27">
@@ -8963,7 +9750,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
